--- a/data.mn/public/datasets/mrpam-petroleum-imports.xlsx
+++ b/data.mn/public/datasets/mrpam-petroleum-imports.xlsx
@@ -10,10 +10,7 @@
     <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'English'!$A$1:$M$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Монгол'!$A$1:$M$67</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -417,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -509,7 +506,6 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>103943</v>
       </c>
@@ -519,7 +515,6 @@
       <c r="F2" t="n">
         <v>42658</v>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1055</v>
       </c>
@@ -546,7 +541,6 @@
       <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
         <v>74722</v>
       </c>
@@ -556,7 +550,6 @@
       <c r="F3" t="n">
         <v>25866</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1316</v>
       </c>
@@ -583,7 +576,6 @@
       <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
         <v>82158</v>
       </c>
@@ -593,7 +585,6 @@
       <c r="F4" t="n">
         <v>28294</v>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>986</v>
       </c>
@@ -620,7 +611,6 @@
       <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
         <v>78651</v>
       </c>
@@ -630,7 +620,6 @@
       <c r="F5" t="n">
         <v>16839</v>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1829</v>
       </c>
@@ -657,7 +646,6 @@
       <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
         <v>52253</v>
       </c>
@@ -667,7 +655,6 @@
       <c r="F6" t="n">
         <v>26219</v>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2427</v>
       </c>
@@ -694,7 +681,6 @@
       <c r="B7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
         <v>99393</v>
       </c>
@@ -704,7 +690,6 @@
       <c r="F7" t="n">
         <v>31340</v>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>1656</v>
       </c>
@@ -731,7 +716,6 @@
       <c r="B8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
         <v>90549</v>
       </c>
@@ -741,11 +725,9 @@
       <c r="F8" t="n">
         <v>46758</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>571</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>1993</v>
       </c>
@@ -766,7 +748,6 @@
       <c r="B9" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
         <v>80081</v>
       </c>
@@ -776,11 +757,9 @@
       <c r="F9" t="n">
         <v>56744</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>5066</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>832</v>
       </c>
@@ -801,7 +780,6 @@
       <c r="B10" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
         <v>63885</v>
       </c>
@@ -811,11 +789,9 @@
       <c r="F10" t="n">
         <v>33935</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>118</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>562</v>
       </c>
@@ -836,7 +812,6 @@
       <c r="B11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
         <v>65044</v>
       </c>
@@ -846,7 +821,6 @@
       <c r="F11" t="n">
         <v>43728</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>5109</v>
       </c>
@@ -873,7 +847,6 @@
       <c r="B12" t="n">
         <v>11</v>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
         <v>86292</v>
       </c>
@@ -883,7 +856,6 @@
       <c r="F12" t="n">
         <v>83990</v>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>3513</v>
       </c>
@@ -910,7 +882,6 @@
       <c r="B13" t="n">
         <v>12</v>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
         <v>99303</v>
       </c>
@@ -920,7 +891,6 @@
       <c r="F13" t="n">
         <v>53674</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>4025</v>
       </c>
@@ -947,7 +917,6 @@
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
         <v>83809</v>
       </c>
@@ -957,11 +926,9 @@
       <c r="F14" t="n">
         <v>39498</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>1769</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
         <v>1805</v>
       </c>
@@ -982,7 +949,6 @@
       <c r="B15" t="n">
         <v>2</v>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
         <v>58792</v>
       </c>
@@ -992,11 +958,9 @@
       <c r="F15" t="n">
         <v>63713</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1244</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
         <v>1492</v>
       </c>
@@ -1017,7 +981,6 @@
       <c r="B16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
         <v>53989</v>
       </c>
@@ -1027,7 +990,6 @@
       <c r="F16" t="n">
         <v>55620</v>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>3876</v>
       </c>
@@ -1054,7 +1016,6 @@
       <c r="B17" t="n">
         <v>4</v>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
         <v>61773</v>
       </c>
@@ -1064,7 +1025,6 @@
       <c r="F17" t="n">
         <v>24945</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>3391</v>
       </c>
@@ -1091,7 +1051,6 @@
       <c r="B18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
         <v>83553</v>
       </c>
@@ -1101,11 +1060,9 @@
       <c r="F18" t="n">
         <v>59583</v>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>1949</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>4245</v>
       </c>
@@ -1126,7 +1083,6 @@
       <c r="B19" t="n">
         <v>6</v>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
         <v>98140</v>
       </c>
@@ -1136,11 +1092,9 @@
       <c r="F19" t="n">
         <v>48840</v>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2075</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>6807</v>
       </c>
@@ -1161,7 +1115,6 @@
       <c r="B20" t="n">
         <v>7</v>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
         <v>66379</v>
       </c>
@@ -1171,11 +1124,9 @@
       <c r="F20" t="n">
         <v>51376</v>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>1271</v>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>1901</v>
       </c>
@@ -1196,7 +1147,6 @@
       <c r="B21" t="n">
         <v>8</v>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
         <v>90955</v>
       </c>
@@ -1206,11 +1156,9 @@
       <c r="F21" t="n">
         <v>44534</v>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>1559</v>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>4277</v>
       </c>
@@ -1231,7 +1179,6 @@
       <c r="B22" t="n">
         <v>9</v>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
         <v>79785</v>
       </c>
@@ -1241,11 +1188,9 @@
       <c r="F22" t="n">
         <v>40452</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>1209</v>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>8062</v>
       </c>
@@ -1266,7 +1211,6 @@
       <c r="B23" t="n">
         <v>10</v>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
         <v>85633</v>
       </c>
@@ -1276,11 +1220,9 @@
       <c r="F23" t="n">
         <v>62672</v>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2008</v>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>3579</v>
       </c>
@@ -1301,7 +1243,6 @@
       <c r="B24" t="n">
         <v>11</v>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
         <v>83260</v>
       </c>
@@ -1311,11 +1252,9 @@
       <c r="F24" t="n">
         <v>73324</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>905</v>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
         <v>6915</v>
       </c>
@@ -1336,7 +1275,6 @@
       <c r="B25" t="n">
         <v>12</v>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
         <v>116402</v>
       </c>
@@ -1346,11 +1284,9 @@
       <c r="F25" t="n">
         <v>52053</v>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>1205</v>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
         <v>3915</v>
       </c>
@@ -1371,7 +1307,6 @@
       <c r="B26" t="n">
         <v>1</v>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
         <v>122435</v>
       </c>
@@ -1381,7 +1316,6 @@
       <c r="F26" t="n">
         <v>29391</v>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>2104</v>
       </c>
@@ -1408,7 +1342,6 @@
       <c r="B27" t="n">
         <v>2</v>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
         <v>71540</v>
       </c>
@@ -1418,7 +1351,6 @@
       <c r="F27" t="n">
         <v>61738</v>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>1463</v>
       </c>
@@ -1445,7 +1377,6 @@
       <c r="B28" t="n">
         <v>3</v>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
         <v>96881</v>
       </c>
@@ -1455,7 +1386,6 @@
       <c r="F28" t="n">
         <v>54079</v>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2012</v>
       </c>
@@ -1482,7 +1412,6 @@
       <c r="B29" t="n">
         <v>4</v>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
         <v>104563</v>
       </c>
@@ -1492,7 +1421,6 @@
       <c r="F29" t="n">
         <v>57674</v>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>486</v>
       </c>
@@ -1519,7 +1447,6 @@
       <c r="B30" t="n">
         <v>5</v>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
         <v>136356</v>
       </c>
@@ -1529,7 +1456,6 @@
       <c r="F30" t="n">
         <v>59760</v>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>1265</v>
       </c>
@@ -1556,7 +1482,6 @@
       <c r="B31" t="n">
         <v>6</v>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
         <v>114638</v>
       </c>
@@ -1566,7 +1491,6 @@
       <c r="F31" t="n">
         <v>65375</v>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>1607</v>
       </c>
@@ -1593,7 +1517,6 @@
       <c r="B32" t="n">
         <v>7</v>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
         <v>139103</v>
       </c>
@@ -1603,7 +1526,6 @@
       <c r="F32" t="n">
         <v>74997</v>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2004</v>
       </c>
@@ -1630,7 +1552,6 @@
       <c r="B33" t="n">
         <v>8</v>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
         <v>152867</v>
       </c>
@@ -1640,7 +1561,6 @@
       <c r="F33" t="n">
         <v>76182</v>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>1754</v>
       </c>
@@ -1667,7 +1587,6 @@
       <c r="B34" t="n">
         <v>9</v>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
         <v>82779</v>
       </c>
@@ -1677,7 +1596,6 @@
       <c r="F34" t="n">
         <v>48141</v>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>606</v>
       </c>
@@ -1704,7 +1622,6 @@
       <c r="B35" t="n">
         <v>10</v>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
         <v>63987</v>
       </c>
@@ -1714,7 +1631,6 @@
       <c r="F35" t="n">
         <v>32141</v>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>2223</v>
       </c>
@@ -1741,7 +1657,6 @@
       <c r="B36" t="n">
         <v>11</v>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
         <v>111213</v>
       </c>
@@ -1751,7 +1666,6 @@
       <c r="F36" t="n">
         <v>64074</v>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>3090</v>
       </c>
@@ -1778,7 +1692,6 @@
       <c r="B37" t="n">
         <v>12</v>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
         <v>146212</v>
       </c>
@@ -1788,7 +1701,6 @@
       <c r="F37" t="n">
         <v>62980</v>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>2479</v>
       </c>
@@ -1815,7 +1727,6 @@
       <c r="B38" t="n">
         <v>1</v>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
         <v>129542</v>
       </c>
@@ -1825,7 +1736,6 @@
       <c r="F38" t="n">
         <v>78421</v>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2492</v>
       </c>
@@ -1852,7 +1762,6 @@
       <c r="B39" t="n">
         <v>2</v>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
         <v>92109</v>
       </c>
@@ -1862,11 +1771,9 @@
       <c r="F39" t="n">
         <v>61289</v>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>1404</v>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
         <v>6326</v>
       </c>
@@ -1887,7 +1794,6 @@
       <c r="B40" t="n">
         <v>3</v>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
         <v>148622</v>
       </c>
@@ -1897,11 +1803,9 @@
       <c r="F40" t="n">
         <v>69149</v>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>1744</v>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
         <v>8136</v>
       </c>
@@ -1922,7 +1826,6 @@
       <c r="B41" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
         <v>140012</v>
       </c>
@@ -1932,11 +1835,9 @@
       <c r="F41" t="n">
         <v>67436</v>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>1194</v>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
         <v>6567</v>
       </c>
@@ -1957,7 +1858,6 @@
       <c r="B42" t="n">
         <v>5</v>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
         <v>140677</v>
       </c>
@@ -1967,11 +1867,9 @@
       <c r="F42" t="n">
         <v>70900</v>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>4487</v>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
         <v>9649</v>
       </c>
@@ -1992,7 +1890,6 @@
       <c r="B43" t="n">
         <v>6</v>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
         <v>118720</v>
       </c>
@@ -2002,11 +1899,9 @@
       <c r="F43" t="n">
         <v>64114</v>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>1240</v>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
         <v>10590</v>
       </c>
@@ -2027,7 +1922,6 @@
       <c r="B44" t="n">
         <v>7</v>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
         <v>146949.3</v>
       </c>
@@ -2037,11 +1931,9 @@
       <c r="F44" t="n">
         <v>71929.2</v>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>318.7</v>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
         <v>10015.4</v>
       </c>
@@ -2062,7 +1954,6 @@
       <c r="B45" t="n">
         <v>8</v>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
         <v>149756.6</v>
       </c>
@@ -2072,11 +1963,9 @@
       <c r="F45" t="n">
         <v>69273.3</v>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>1540.8</v>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
         <v>6265.4</v>
       </c>
@@ -2097,7 +1986,6 @@
       <c r="B46" t="n">
         <v>9</v>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
         <v>142138.4</v>
       </c>
@@ -2107,11 +1995,9 @@
       <c r="F46" t="n">
         <v>66267.8</v>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>572.3</v>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
         <v>2953.8</v>
       </c>
@@ -2132,7 +2018,6 @@
       <c r="B47" t="n">
         <v>10</v>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
         <v>127371.3</v>
       </c>
@@ -2142,11 +2027,9 @@
       <c r="F47" t="n">
         <v>64950.9</v>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>462.9</v>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
         <v>9803.6</v>
       </c>
@@ -2167,7 +2050,6 @@
       <c r="B48" t="n">
         <v>11</v>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
         <v>120365.6</v>
       </c>
@@ -2177,11 +2059,9 @@
       <c r="F48" t="n">
         <v>79455.8</v>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>844.8</v>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
         <v>5143.9</v>
       </c>
@@ -2202,7 +2082,6 @@
       <c r="B49" t="n">
         <v>12</v>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
         <v>161342</v>
       </c>
@@ -2212,11 +2091,9 @@
       <c r="F49" t="n">
         <v>102823</v>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>2905</v>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
         <v>11363</v>
       </c>
@@ -2237,7 +2114,6 @@
       <c r="B50" t="n">
         <v>1</v>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
         <v>183926</v>
       </c>
@@ -2247,11 +2123,9 @@
       <c r="F50" t="n">
         <v>90482</v>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>1487</v>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
         <v>10152</v>
       </c>
@@ -2272,7 +2146,6 @@
       <c r="B51" t="n">
         <v>2</v>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
         <v>154191</v>
       </c>
@@ -2282,11 +2155,9 @@
       <c r="F51" t="n">
         <v>66749</v>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>1467</v>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
         <v>5092</v>
       </c>
@@ -2307,7 +2178,6 @@
       <c r="B52" t="n">
         <v>3</v>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
         <v>127439</v>
       </c>
@@ -2317,11 +2187,9 @@
       <c r="F52" t="n">
         <v>67438</v>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>1950</v>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
         <v>8241</v>
       </c>
@@ -2342,7 +2210,6 @@
       <c r="B53" t="n">
         <v>4</v>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
         <v>140578</v>
       </c>
@@ -2352,11 +2219,9 @@
       <c r="F53" t="n">
         <v>48497</v>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>339</v>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
         <v>11201</v>
       </c>
@@ -2377,7 +2242,6 @@
       <c r="B54" t="n">
         <v>5</v>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
         <v>112022</v>
       </c>
@@ -2387,11 +2251,9 @@
       <c r="F54" t="n">
         <v>58478</v>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>1401</v>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
         <v>2624</v>
       </c>
@@ -2412,7 +2274,6 @@
       <c r="B55" t="n">
         <v>6</v>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
         <v>125025</v>
       </c>
@@ -2422,11 +2283,9 @@
       <c r="F55" t="n">
         <v>68871</v>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>694</v>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
         <v>7201</v>
       </c>
@@ -2447,19 +2306,15 @@
       <c r="B56" t="n">
         <v>7</v>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
         <v>153359</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="n">
         <v>76949</v>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>1376</v>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
         <v>6512</v>
       </c>
@@ -2480,19 +2335,15 @@
       <c r="B57" t="n">
         <v>8</v>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
         <v>199924</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
         <v>70337</v>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>1188</v>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
         <v>10770</v>
       </c>
@@ -2513,19 +2364,15 @@
       <c r="B58" t="n">
         <v>9</v>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
         <v>164054</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
         <v>70444</v>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>2704</v>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
         <v>3173</v>
       </c>
@@ -2546,19 +2393,15 @@
       <c r="B59" t="n">
         <v>10</v>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
         <v>138853</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
         <v>58721</v>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>563</v>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
         <v>4378</v>
       </c>
@@ -2579,19 +2422,15 @@
       <c r="B60" t="n">
         <v>11</v>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
         <v>129576</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
         <v>71445</v>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>2425</v>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
         <v>4888</v>
       </c>
@@ -2612,19 +2451,15 @@
       <c r="B61" t="n">
         <v>12</v>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
         <v>205572</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
         <v>79746</v>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>4944</v>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
         <v>11420</v>
       </c>
@@ -2645,19 +2480,15 @@
       <c r="B62" t="n">
         <v>1</v>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="n">
         <v>145938</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
         <v>108024</v>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>3043</v>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
         <v>3078</v>
       </c>
@@ -2684,7 +2515,6 @@
       <c r="D63" t="n">
         <v>130546</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
         <v>90870</v>
       </c>
@@ -2694,7 +2524,6 @@
       <c r="H63" t="n">
         <v>2733</v>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="n">
         <v>5406</v>
       </c>
@@ -2721,7 +2550,6 @@
       <c r="D64" t="n">
         <v>144131</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
         <v>81106</v>
       </c>
@@ -2731,7 +2559,6 @@
       <c r="H64" t="n">
         <v>4547</v>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
         <v>6197</v>
       </c>
@@ -2758,7 +2585,6 @@
       <c r="D65" t="n">
         <v>146027</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
         <v>49862</v>
       </c>
@@ -2768,7 +2594,6 @@
       <c r="H65" t="n">
         <v>1794</v>
       </c>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
         <v>11588</v>
       </c>
@@ -2795,7 +2620,6 @@
       <c r="D66" t="n">
         <v>118622</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
         <v>67787</v>
       </c>
@@ -2805,7 +2629,6 @@
       <c r="H66" t="n">
         <v>913</v>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
         <v>8883</v>
       </c>
@@ -2832,15 +2655,12 @@
       <c r="D67" t="n">
         <v>114874</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
         <v>57353</v>
       </c>
       <c r="G67" t="n">
         <v>521</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
         <v>5253</v>
       </c>
@@ -2854,8 +2674,42 @@
         <v>221575</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" t="n">
+        <v>13911</v>
+      </c>
+      <c r="D68" t="n">
+        <v>118849</v>
+      </c>
+      <c r="F68" t="n">
+        <v>46562</v>
+      </c>
+      <c r="G68" t="n">
+        <v>526</v>
+      </c>
+      <c r="H68" t="n">
+        <v>617</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2112</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2367</v>
+      </c>
+      <c r="L68" t="n">
+        <v>18348</v>
+      </c>
+      <c r="M68" t="n">
+        <v>203292</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2866,7 +2720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2958,7 +2812,6 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>3434</v>
       </c>
@@ -2977,7 +2830,6 @@
       <c r="I2" t="n">
         <v>103943</v>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>165861</v>
       </c>
@@ -2995,7 +2847,6 @@
       <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
         <v>3511</v>
       </c>
@@ -3014,7 +2865,6 @@
       <c r="I3" t="n">
         <v>74722</v>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
         <v>121367</v>
       </c>
@@ -3032,7 +2882,6 @@
       <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
         <v>5152</v>
       </c>
@@ -3051,7 +2900,6 @@
       <c r="I4" t="n">
         <v>82158</v>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>152830</v>
       </c>
@@ -3069,7 +2917,6 @@
       <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
         <v>4241</v>
       </c>
@@ -3088,7 +2935,6 @@
       <c r="I5" t="n">
         <v>78651</v>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>131984</v>
       </c>
@@ -3106,7 +2952,6 @@
       <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
         <v>5076</v>
       </c>
@@ -3125,7 +2970,6 @@
       <c r="I6" t="n">
         <v>52253</v>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>104381</v>
       </c>
@@ -3143,7 +2987,6 @@
       <c r="B7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
         <v>7994</v>
       </c>
@@ -3162,7 +3005,6 @@
       <c r="I7" t="n">
         <v>99393</v>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>167237</v>
       </c>
@@ -3180,7 +3022,6 @@
       <c r="B8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
         <v>3787</v>
       </c>
@@ -3190,14 +3031,12 @@
       <c r="F8" t="n">
         <v>571</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>27098</v>
       </c>
       <c r="I8" t="n">
         <v>90549</v>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
         <v>170998</v>
       </c>
@@ -3215,7 +3054,6 @@
       <c r="B9" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
         <v>4236</v>
       </c>
@@ -3225,14 +3063,12 @@
       <c r="F9" t="n">
         <v>5066</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>4340</v>
       </c>
       <c r="I9" t="n">
         <v>80081</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
         <v>154815</v>
       </c>
@@ -3250,7 +3086,6 @@
       <c r="B10" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
         <v>4960</v>
       </c>
@@ -3260,14 +3095,12 @@
       <c r="F10" t="n">
         <v>118</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>7640</v>
       </c>
       <c r="I10" t="n">
         <v>63885</v>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>112997</v>
       </c>
@@ -3285,7 +3118,6 @@
       <c r="B11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
         <v>436</v>
       </c>
@@ -3304,7 +3136,6 @@
       <c r="I11" t="n">
         <v>65044</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
         <v>130991</v>
       </c>
@@ -3322,7 +3153,6 @@
       <c r="B12" t="n">
         <v>11</v>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
         <v>10129</v>
       </c>
@@ -3341,7 +3171,6 @@
       <c r="I12" t="n">
         <v>86292</v>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>203881</v>
       </c>
@@ -3359,7 +3188,6 @@
       <c r="B13" t="n">
         <v>12</v>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
         <v>5672</v>
       </c>
@@ -3378,7 +3206,6 @@
       <c r="I13" t="n">
         <v>99303</v>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>189533</v>
       </c>
@@ -3396,7 +3223,6 @@
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
         <v>1229</v>
       </c>
@@ -3406,14 +3232,12 @@
       <c r="F14" t="n">
         <v>1769</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>9317</v>
       </c>
       <c r="I14" t="n">
         <v>83809</v>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
         <v>139456</v>
       </c>
@@ -3431,7 +3255,6 @@
       <c r="B15" t="n">
         <v>2</v>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
         <v>4187</v>
       </c>
@@ -3441,14 +3264,12 @@
       <c r="F15" t="n">
         <v>1244</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>6588</v>
       </c>
       <c r="I15" t="n">
         <v>58792</v>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
         <v>138921</v>
       </c>
@@ -3466,7 +3287,6 @@
       <c r="B16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
         <v>4821</v>
       </c>
@@ -3485,7 +3305,6 @@
       <c r="I16" t="n">
         <v>53989</v>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
         <v>133828</v>
       </c>
@@ -3503,7 +3322,6 @@
       <c r="B17" t="n">
         <v>4</v>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
         <v>2254</v>
       </c>
@@ -3522,7 +3340,6 @@
       <c r="I17" t="n">
         <v>61773</v>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
         <v>114043</v>
       </c>
@@ -3540,7 +3357,6 @@
       <c r="B18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
         <v>2382</v>
       </c>
@@ -3550,14 +3366,12 @@
       <c r="F18" t="n">
         <v>1949</v>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>17178</v>
       </c>
       <c r="I18" t="n">
         <v>83553</v>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
         <v>172740</v>
       </c>
@@ -3575,7 +3389,6 @@
       <c r="B19" t="n">
         <v>6</v>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
         <v>4036</v>
       </c>
@@ -3585,14 +3398,12 @@
       <c r="F19" t="n">
         <v>2075</v>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>23969</v>
       </c>
       <c r="I19" t="n">
         <v>98140</v>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
         <v>187104</v>
       </c>
@@ -3610,7 +3421,6 @@
       <c r="B20" t="n">
         <v>7</v>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
         <v>741</v>
       </c>
@@ -3620,14 +3430,12 @@
       <c r="F20" t="n">
         <v>1271</v>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>11915</v>
       </c>
       <c r="I20" t="n">
         <v>66379</v>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
         <v>136573</v>
       </c>
@@ -3645,7 +3453,6 @@
       <c r="B21" t="n">
         <v>8</v>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
         <v>6911</v>
       </c>
@@ -3655,14 +3462,12 @@
       <c r="F21" t="n">
         <v>1559</v>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>9413</v>
       </c>
       <c r="I21" t="n">
         <v>90955</v>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
         <v>166937</v>
       </c>
@@ -3680,7 +3485,6 @@
       <c r="B22" t="n">
         <v>9</v>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
         <v>1292</v>
       </c>
@@ -3690,14 +3494,12 @@
       <c r="F22" t="n">
         <v>1209</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>20821</v>
       </c>
       <c r="I22" t="n">
         <v>79785</v>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
         <v>153678</v>
       </c>
@@ -3715,7 +3517,6 @@
       <c r="B23" t="n">
         <v>10</v>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
         <v>932</v>
       </c>
@@ -3725,14 +3526,12 @@
       <c r="F23" t="n">
         <v>2008</v>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>7913</v>
       </c>
       <c r="I23" t="n">
         <v>85633</v>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
         <v>164335</v>
       </c>
@@ -3750,7 +3549,6 @@
       <c r="B24" t="n">
         <v>11</v>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
         <v>2891</v>
       </c>
@@ -3760,14 +3558,12 @@
       <c r="F24" t="n">
         <v>905</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>3531</v>
       </c>
       <c r="I24" t="n">
         <v>83260</v>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
         <v>175240</v>
       </c>
@@ -3785,7 +3581,6 @@
       <c r="B25" t="n">
         <v>12</v>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
         <v>840</v>
       </c>
@@ -3795,14 +3590,12 @@
       <c r="F25" t="n">
         <v>1205</v>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>13772</v>
       </c>
       <c r="I25" t="n">
         <v>116402</v>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
         <v>192488</v>
       </c>
@@ -3820,7 +3613,6 @@
       <c r="B26" t="n">
         <v>1</v>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
         <v>2351</v>
       </c>
@@ -3839,7 +3631,6 @@
       <c r="I26" t="n">
         <v>122435</v>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
         <v>168935</v>
       </c>
@@ -3857,7 +3648,6 @@
       <c r="B27" t="n">
         <v>2</v>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
         <v>1440</v>
       </c>
@@ -3876,7 +3666,6 @@
       <c r="I27" t="n">
         <v>71540</v>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
         <v>153583</v>
       </c>
@@ -3894,7 +3683,6 @@
       <c r="B28" t="n">
         <v>3</v>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
         <v>2474</v>
       </c>
@@ -3913,7 +3701,6 @@
       <c r="I28" t="n">
         <v>96881</v>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="n">
         <v>179102</v>
       </c>
@@ -3931,7 +3718,6 @@
       <c r="B29" t="n">
         <v>4</v>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
         <v>1032</v>
       </c>
@@ -3950,7 +3736,6 @@
       <c r="I29" t="n">
         <v>104563</v>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
         <v>192367</v>
       </c>
@@ -3968,7 +3753,6 @@
       <c r="B30" t="n">
         <v>5</v>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
         <v>1695</v>
       </c>
@@ -3987,7 +3771,6 @@
       <c r="I30" t="n">
         <v>136356</v>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
         <v>233854</v>
       </c>
@@ -4005,7 +3788,6 @@
       <c r="B31" t="n">
         <v>6</v>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
         <v>2751</v>
       </c>
@@ -4024,7 +3806,6 @@
       <c r="I31" t="n">
         <v>114638</v>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
         <v>218606</v>
       </c>
@@ -4042,7 +3823,6 @@
       <c r="B32" t="n">
         <v>7</v>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
         <v>2795</v>
       </c>
@@ -4061,7 +3841,6 @@
       <c r="I32" t="n">
         <v>139103</v>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
         <v>262698</v>
       </c>
@@ -4079,7 +3858,6 @@
       <c r="B33" t="n">
         <v>8</v>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
         <v>4582</v>
       </c>
@@ -4098,7 +3876,6 @@
       <c r="I33" t="n">
         <v>152867</v>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
         <v>272540</v>
       </c>
@@ -4116,7 +3893,6 @@
       <c r="B34" t="n">
         <v>9</v>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
         <v>1452</v>
       </c>
@@ -4135,7 +3911,6 @@
       <c r="I34" t="n">
         <v>82779</v>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="n">
         <v>158754</v>
       </c>
@@ -4153,7 +3928,6 @@
       <c r="B35" t="n">
         <v>10</v>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
         <v>0</v>
       </c>
@@ -4172,7 +3946,6 @@
       <c r="I35" t="n">
         <v>63987</v>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
         <v>147865</v>
       </c>
@@ -4190,7 +3963,6 @@
       <c r="B36" t="n">
         <v>11</v>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
         <v>0</v>
       </c>
@@ -4209,7 +3981,6 @@
       <c r="I36" t="n">
         <v>111213</v>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
         <v>201024</v>
       </c>
@@ -4227,7 +3998,6 @@
       <c r="B37" t="n">
         <v>12</v>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
         <v>992</v>
       </c>
@@ -4246,7 +4016,6 @@
       <c r="I37" t="n">
         <v>146212</v>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
         <v>228157</v>
       </c>
@@ -4264,7 +4033,6 @@
       <c r="B38" t="n">
         <v>1</v>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
         <v>1740</v>
       </c>
@@ -4283,7 +4051,6 @@
       <c r="I38" t="n">
         <v>129542</v>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
         <v>231404</v>
       </c>
@@ -4301,7 +4068,6 @@
       <c r="B39" t="n">
         <v>2</v>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
         <v>0</v>
       </c>
@@ -4311,14 +4077,12 @@
       <c r="F39" t="n">
         <v>1404</v>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>5698</v>
       </c>
       <c r="I39" t="n">
         <v>92109</v>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="n">
         <v>171587</v>
       </c>
@@ -4336,7 +4100,6 @@
       <c r="B40" t="n">
         <v>3</v>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
         <v>308</v>
       </c>
@@ -4346,14 +4109,12 @@
       <c r="F40" t="n">
         <v>1744</v>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>7804</v>
       </c>
       <c r="I40" t="n">
         <v>148622</v>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
         <v>240548</v>
       </c>
@@ -4371,7 +4132,6 @@
       <c r="B41" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
         <v>128</v>
       </c>
@@ -4381,14 +4141,12 @@
       <c r="F41" t="n">
         <v>1194</v>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>10258</v>
       </c>
       <c r="I41" t="n">
         <v>140012</v>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
         <v>228537</v>
       </c>
@@ -4406,7 +4164,6 @@
       <c r="B42" t="n">
         <v>5</v>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
         <v>164</v>
       </c>
@@ -4416,14 +4173,12 @@
       <c r="F42" t="n">
         <v>4487</v>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>14379</v>
       </c>
       <c r="I42" t="n">
         <v>140677</v>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
         <v>243046</v>
       </c>
@@ -4441,7 +4196,6 @@
       <c r="B43" t="n">
         <v>6</v>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
         <v>1095</v>
       </c>
@@ -4451,14 +4205,12 @@
       <c r="F43" t="n">
         <v>1240</v>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>10820</v>
       </c>
       <c r="I43" t="n">
         <v>118720</v>
       </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
         <v>209033</v>
       </c>
@@ -4476,7 +4228,6 @@
       <c r="B44" t="n">
         <v>7</v>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
         <v>58.4</v>
       </c>
@@ -4486,14 +4237,12 @@
       <c r="F44" t="n">
         <v>318.7</v>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>16812.7</v>
       </c>
       <c r="I44" t="n">
         <v>146949.3</v>
       </c>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="n">
         <v>251174</v>
       </c>
@@ -4511,7 +4260,6 @@
       <c r="B45" t="n">
         <v>8</v>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
         <v>417.9</v>
       </c>
@@ -4521,14 +4269,12 @@
       <c r="F45" t="n">
         <v>1540.8</v>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>22181.1</v>
       </c>
       <c r="I45" t="n">
         <v>149756.6</v>
       </c>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="n">
         <v>252918</v>
       </c>
@@ -4546,7 +4292,6 @@
       <c r="B46" t="n">
         <v>9</v>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
         <v>860.9</v>
       </c>
@@ -4556,14 +4301,12 @@
       <c r="F46" t="n">
         <v>572.3</v>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>24475.2</v>
       </c>
       <c r="I46" t="n">
         <v>142138.4</v>
       </c>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="n">
         <v>242019</v>
       </c>
@@ -4581,7 +4324,6 @@
       <c r="B47" t="n">
         <v>10</v>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
         <v>70.40000000000001</v>
       </c>
@@ -4591,14 +4333,12 @@
       <c r="F47" t="n">
         <v>462.9</v>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>19461.2</v>
       </c>
       <c r="I47" t="n">
         <v>127371.3</v>
       </c>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
         <v>227244</v>
       </c>
@@ -4616,7 +4356,6 @@
       <c r="B48" t="n">
         <v>11</v>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
         <v>751.9</v>
       </c>
@@ -4626,14 +4365,12 @@
       <c r="F48" t="n">
         <v>844.8</v>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>7627.3</v>
       </c>
       <c r="I48" t="n">
         <v>120365.6</v>
       </c>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="n">
         <v>217162</v>
       </c>
@@ -4651,7 +4388,6 @@
       <c r="B49" t="n">
         <v>12</v>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
         <v>44</v>
       </c>
@@ -4661,14 +4397,12 @@
       <c r="F49" t="n">
         <v>2905</v>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>11235</v>
       </c>
       <c r="I49" t="n">
         <v>161342</v>
       </c>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="n">
         <v>293457</v>
       </c>
@@ -4686,7 +4420,6 @@
       <c r="B50" t="n">
         <v>1</v>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
         <v>66</v>
       </c>
@@ -4696,14 +4429,12 @@
       <c r="F50" t="n">
         <v>1487</v>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>6071</v>
       </c>
       <c r="I50" t="n">
         <v>183926</v>
       </c>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="n">
         <v>296382</v>
       </c>
@@ -4721,7 +4452,6 @@
       <c r="B51" t="n">
         <v>2</v>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
         <v>56</v>
       </c>
@@ -4731,14 +4461,12 @@
       <c r="F51" t="n">
         <v>1467</v>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>6042</v>
       </c>
       <c r="I51" t="n">
         <v>154191</v>
       </c>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="n">
         <v>236383</v>
       </c>
@@ -4756,7 +4484,6 @@
       <c r="B52" t="n">
         <v>3</v>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
         <v>131</v>
       </c>
@@ -4766,14 +4493,12 @@
       <c r="F52" t="n">
         <v>1950</v>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>6480</v>
       </c>
       <c r="I52" t="n">
         <v>127439</v>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="n">
         <v>216299</v>
       </c>
@@ -4791,7 +4516,6 @@
       <c r="B53" t="n">
         <v>4</v>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
         <v>0</v>
       </c>
@@ -4801,14 +4525,12 @@
       <c r="F53" t="n">
         <v>339</v>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>15853</v>
       </c>
       <c r="I53" t="n">
         <v>140578</v>
       </c>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="n">
         <v>219425</v>
       </c>
@@ -4826,7 +4548,6 @@
       <c r="B54" t="n">
         <v>5</v>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
         <v>0</v>
       </c>
@@ -4836,14 +4557,12 @@
       <c r="F54" t="n">
         <v>1401</v>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>17850</v>
       </c>
       <c r="I54" t="n">
         <v>112022</v>
       </c>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="n">
         <v>195699</v>
       </c>
@@ -4861,7 +4580,6 @@
       <c r="B55" t="n">
         <v>6</v>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
         <v>0</v>
       </c>
@@ -4871,14 +4589,12 @@
       <c r="F55" t="n">
         <v>694</v>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>24463</v>
       </c>
       <c r="I55" t="n">
         <v>125025</v>
       </c>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="n">
         <v>227332</v>
       </c>
@@ -4896,22 +4612,18 @@
       <c r="B56" t="n">
         <v>7</v>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
         <v>76949</v>
       </c>
       <c r="F56" t="n">
         <v>1376</v>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>16140</v>
       </c>
       <c r="I56" t="n">
         <v>153359</v>
       </c>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="n">
         <v>259693</v>
       </c>
@@ -4929,22 +4641,18 @@
       <c r="B57" t="n">
         <v>8</v>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
         <v>70337</v>
       </c>
       <c r="F57" t="n">
         <v>1188</v>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>18454</v>
       </c>
       <c r="I57" t="n">
         <v>199924</v>
       </c>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="n">
         <v>307239</v>
       </c>
@@ -4962,22 +4670,18 @@
       <c r="B58" t="n">
         <v>9</v>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
         <v>70444</v>
       </c>
       <c r="F58" t="n">
         <v>2704</v>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>19944</v>
       </c>
       <c r="I58" t="n">
         <v>164054</v>
       </c>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="n">
         <v>268427</v>
       </c>
@@ -4995,22 +4699,18 @@
       <c r="B59" t="n">
         <v>10</v>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
         <v>58721</v>
       </c>
       <c r="F59" t="n">
         <v>563</v>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>13393</v>
       </c>
       <c r="I59" t="n">
         <v>138853</v>
       </c>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
         <v>219147</v>
       </c>
@@ -5028,22 +4728,18 @@
       <c r="B60" t="n">
         <v>11</v>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
         <v>71445</v>
       </c>
       <c r="F60" t="n">
         <v>2425</v>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>6149</v>
       </c>
       <c r="I60" t="n">
         <v>129576</v>
       </c>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="n">
         <v>217609</v>
       </c>
@@ -5061,22 +4757,18 @@
       <c r="B61" t="n">
         <v>12</v>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
         <v>79746</v>
       </c>
       <c r="F61" t="n">
         <v>4944</v>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>3912</v>
       </c>
       <c r="I61" t="n">
         <v>205572</v>
       </c>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
         <v>309380</v>
       </c>
@@ -5094,22 +4786,18 @@
       <c r="B62" t="n">
         <v>1</v>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
         <v>108024</v>
       </c>
       <c r="F62" t="n">
         <v>3043</v>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>3715</v>
       </c>
       <c r="I62" t="n">
         <v>145938</v>
       </c>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="n">
         <v>267852</v>
       </c>
@@ -5130,14 +4818,12 @@
       <c r="C63" t="n">
         <v>18218</v>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
         <v>90870</v>
       </c>
       <c r="F63" t="n">
         <v>2733</v>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>2517</v>
       </c>
@@ -5167,14 +4853,12 @@
       <c r="C64" t="n">
         <v>14033</v>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
         <v>81106</v>
       </c>
       <c r="F64" t="n">
         <v>4547</v>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>7075</v>
       </c>
@@ -5204,14 +4888,12 @@
       <c r="C65" t="n">
         <v>6401</v>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
         <v>49862</v>
       </c>
       <c r="F65" t="n">
         <v>1794</v>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>14453</v>
       </c>
@@ -5241,14 +4923,12 @@
       <c r="C66" t="n">
         <v>3352</v>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
         <v>67787</v>
       </c>
       <c r="F66" t="n">
         <v>913</v>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>16975</v>
       </c>
@@ -5278,12 +4958,9 @@
       <c r="C67" t="n">
         <v>521</v>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
         <v>57353</v>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>17957</v>
       </c>
@@ -5303,8 +4980,42 @@
         <v>4043</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" t="n">
+        <v>526</v>
+      </c>
+      <c r="E68" t="n">
+        <v>46562</v>
+      </c>
+      <c r="F68" t="n">
+        <v>617</v>
+      </c>
+      <c r="H68" t="n">
+        <v>18348</v>
+      </c>
+      <c r="I68" t="n">
+        <v>118849</v>
+      </c>
+      <c r="J68" t="n">
+        <v>13911</v>
+      </c>
+      <c r="K68" t="n">
+        <v>203292</v>
+      </c>
+      <c r="L68" t="n">
+        <v>2112</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2367</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>